--- a/01_Docs/Visa-Landing-Page_Tai_lieu.xlsx
+++ b/01_Docs/Visa-Landing-Page_Tai_lieu.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Công nghệ" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Deploy" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Bàn giao Claude Code" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Nội dung Đăng bài" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -787,7 +788,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>6 phase, checklist nghiệm thu, 14 test case</t>
+          <t>6 phase, checklist nghiệm thu, test case</t>
         </is>
       </c>
     </row>
@@ -842,80 +843,97 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>09_Nội dung Đăng bài</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Thư viện nội dung thu thập từ Facebook + spec tính năng Trang Blog công khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Chú thích màu dùng trong file</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Màu</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="29" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="29" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Đỏ</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Ưu tiên/Impact CAO – cần xử lý trước</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Vàng</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Ưu tiên/Impact TRUNG BÌNH</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Xám</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Ưu tiên/Impact THẤP</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="29" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="29" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Xanh lá</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Đã hoàn thành</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Lưu ý: sơ đồ trực quan (Mermaid) và wireframe ASCII chi tiết vẫn xem tốt nhất trong các file .md tại folder 01_Docs.</t>
         </is>
@@ -924,10 +942,1134 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>09. THƯ VIỆN NỘI DUNG FACEBOOK &amp; SPEC TRANG BLOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ tài liệu — KHÔNG kèm code | Nguồn: Facebook 'Chuyên Visa Nhật Bản - toàn quốc' | Khảo sát 2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Nguồn dữ liệu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Trang</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Vai trò</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả khảo sát</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="101.5" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Chuyên Visa Nhật Bản - toàn quốc</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Trang công ty (Facebook Page)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>1,3K theo dõi, 2 đánh giá thật, nhiều album ảnh + bài marketing</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Aki Hiền (cá nhân)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Facebook cá nhân tư vấn viên</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ có nội dung đời sống — KHÔNG dùng làm nguồn nội dung</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>1. Kiểm kê nội dung đã thu thập</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Loại nội dung</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Tóm tắt (đã diễn giải lại)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Ngày gốc</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Đề xuất dùng cho</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="43.5" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Đánh giá khách hàng thật</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2 đánh giá 'đề xuất': khách khen thủ tục nhanh gọn/dịch vụ tốt; khách khen nhân viên nhiệt tình, ra visa nhanh</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>06/2022, 08/2025</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Slider 'Khách hàng nói gì' trên index.html</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>✅ Đã dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="43.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Album 'Khám phá Nhật Bản'</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Ảnh phong cảnh Nhật Bản (Phú Sĩ, Shibuya/Dotonbori về đêm, chùa cổ, mùa lá đỏ) + caption ngắn truyền cảm hứng</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Gần đây</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Ảnh minh họa blog / mạng xã hội</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ Cần xem lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="29" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Bài 'VISA NHẬT BẢN – CHẠM TAY ĐẾN...'</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Bài giới thiệu dịch vụ cảm xúc, gắn nhãn 'Nội dung do AI tạo'</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Gần đây</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Viết lại bản riêng cho blog (mục 2, bài #2)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ Cần xem lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="29" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Bài hỏi mở về du lịch Nhật Bản</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Câu hỏi mở dẫn dắt vào dịch vụ tư vấn</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Gần đây</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Ý tưởng bài blog #1 (hướng dẫn người mới)</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ Cần xem lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="43.5" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Album 'Visa khách iu'</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Ảnh visa/hộ chiếu đã đậu, che thông tin cá nhân + banner liên hệ đè lên</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Nhiều thời điểm</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Ảnh 'bằng chứng thành công' cho blog/mạng xã hội</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ Cần xem lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="43.5" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Banner cover trang</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Thông điệp cốt lõi: tư vấn hoàn thiện hồ sơ, xử lý trọn gói, đậu mới thanh toán, nhận toàn quốc</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Đã khớp với USP hiện có trên landing page</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>✅ Đã dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2. Đề xuất 3 bài viết mới (Claude soạn mới — không sao chép bài gốc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Bài</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Tiêu đề</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Nội dung tóm tắt</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Danh mục</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Ảnh đề xuất</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="43.5" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Lần đầu xin visa Nhật Bản? 4 bước bạn cần biết</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Hướng dẫn theo đúng quy trình 4 bước đã có trên landing page + giấy tờ cơ bản + nhắc chính sách đậu mới thu phí</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm xin visa</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Ảnh hộ chiếu/vé máy bay có bản quyền rõ ràng</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>☐ Chưa duyệt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="43.5" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Vì sao ngày càng nhiều người Đà Nẵng chọn Nhật Bản</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Bài truyền cảm hứng du lịch, dẫn nhẹ sang thông điệp đồng hành cùng Top Visa — không số liệu tự bịa</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Tin tức</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Ảnh phong cảnh Nhật Bản có giấy phép hợp lệ</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>☐ Chưa duyệt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="43.5" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Cam kết 'Đậu Visa Mới Thu Phí Dịch Vụ' nghĩa là gì?</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Giải thích rõ chính sách: chỉ thu phí dịch vụ khi đậu; phí lãnh sự riêng, không hoàn lại</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Khuyến mãi</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Dùng lại banner cam kết có sẵn trên landing page</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>☐ Chưa duyệt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Cách dùng: dán 3 bài trên vào Tab Bài viết trong admin.html (chức năng FR-13 đã có sẵn) sau khi bạn duyệt/chỉnh nội dung — không cần code thêm để đăng bài.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>3. Spec chức năng: Trang Blog công khai (cho Claude Code)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>O4 trong 01_Yêu cầu đang ở diện 'Ngoài phạm vi'. Đề xuất đưa phần HIỂN THỊ blog công khai vào triển khai — KHÔNG cần đổi schema vì bảng posts/categories + RLS cho anon SELECT khi published=true đã có sẵn trong supabase_setup.sql.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Yêu cầu</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="43.5" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>BLOG-01</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Trang danh sách bài viết</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>File mới blog.html — grid card (ảnh, tiêu đề, danh mục, ngày, trích đoạn), chỉ bài published=true, mới nhất trước</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="29" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>BLOG-02</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Lọc theo danh mục</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Dropdown/tab lọc theo bảng categories có sẵn</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="29" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>BLOG-03</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Trang chi tiết bài viết</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>blog.html?id=... — hiển thị đầy đủ content, ảnh, ngày; nút quay lại</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="29" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>BLOG-04</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Liên kết 2 chiều với landing page</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Thêm mục Blog vào navbar index.html; cuối bài có CTA quay lại #dang-ky</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="29" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>BLOG-05</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>SEO cơ bản</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>title/meta description set động bằng JS sau khi fetch dữ liệu</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="29" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>BLOG-06</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái rỗng</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có bài published=true → thông báo thân thiện, không phải trang trắng</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Ràng buộc kỹ thuật (giữ đúng CLAUDE.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Ràng buộc</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>HTML/CSS/JS thuần, không framework/build step — giống index.html/admin.html</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="72.5" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Copy nguyên khối :root{...} CSS variables từ index.html, không tạo bộ màu mới</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Dùng đúng SUPABASE_URL/SUPABASE_ANON_KEY theo cách index.html đang khai báo</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="72.5" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ SELECT — không có form ghi dữ liệu ở blog.html, không cần thêm RLS policy mới</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Test case đề xuất (bổ sung vào sheet 05 khi triển khai)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="43.5" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>TC-B01</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Có ≥1 bài published=true</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Mở blog.html</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Thấy danh sách bài, mới nhất trên đầu</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>TC-B02</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có bài nào published</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Mở blog.html</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Hiện thông báo 'Chưa có bài viết', không lỗi console</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="43.5" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>TC-B03</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Đang xem blog.html</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Bấm 1 bài</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Chuyển sang trang chi tiết đúng nội dung</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="29" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>TC-B04</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Đang xem trang chi tiết</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Bấm 'Quay lại'</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Về đúng danh sách</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48" ht="43.5" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>TC-B05</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Trên mobile</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Mở blog.html</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Grid 1 cột, ảnh không vỡ layout</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>⚠ Rà soát</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Vấn đề</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Đề xuất</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Loại</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="72.5" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Ảnh phong cảnh Nhật Bản trên Facebook nhiều khả năng là ảnh sưu tầm/stock, chưa rõ bản quyền</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>KHÔNG tự tải/dùng lại; xác minh nguồn gốc hoặc thay bằng ảnh có giấy phép (Unsplash/Pexels) hoặc ảnh tự chụp</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="43.5" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ có 2 đánh giá công khai trên Facebook</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Chủ động xin thêm đánh giá từ khách đã dùng dịch vụ</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="43.5" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Bài 'VISA NHẬT BẢN – CHẠM TAY...' gắn nhãn AI-generated</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Không tái sử dụng nguyên caption — đã viết lại riêng ở bài #2</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="43.5" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Ảnh 'Visa khách iu' còn thông tin khách dù đã che</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Xin phép khách thêm lần nữa trước khi dùng ở kênh mới; che kỹ toàn bộ passport/tên</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="43.5" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Facebook cá nhân tư vấn viên không có nội dung phù hợp</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Không dùng làm nguồn; lập quy trình xin khách gửi review trực tiếp thay vì lấy từ MXH cá nhân</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="72.5" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Đưa O4 (Blog) từ ngoài phạm vi sang triển khai phát sinh thời gian ngoài kế hoạch gốc</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Coi là Phase 6.5 — làm sau khi Phase 1-6 gốc ổn định</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -939,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1465,7 +2607,7 @@
       <c r="E28" s="6" t="inlineStr"/>
       <c r="F28" s="6" t="inlineStr"/>
     </row>
-    <row r="29" ht="16" customHeight="1">
+    <row r="29" ht="29" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>O4</t>
@@ -1478,12 +2620,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Phase mở rộng</t>
+          <t>Xem sheet 09 — đề xuất đưa 1 phần vào triển khai</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Ngoài</t>
+          <t>Ngoài*</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
@@ -1616,7 +2758,7 @@
       <c r="E36" s="6" t="inlineStr"/>
       <c r="F36" s="6" t="inlineStr"/>
     </row>
-    <row r="37" ht="16" customHeight="1">
+    <row r="37" ht="29" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>FR-05</t>
@@ -1629,7 +2771,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Grid 3–6 review</t>
+          <t>Slider bấm Next/Prev, dữ liệu thật từ Facebook</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -1856,414 +2998,438 @@
       <c r="E46" s="6" t="inlineStr"/>
       <c r="F46" s="6" t="inlineStr"/>
     </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="47" ht="29" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>FR-15</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Trang Blog công khai</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Hiển thị bài viết đã published — xem chi tiết sheet 09</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>5. Yêu cầu phi chức năng (Non-functional Requirements)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Yêu cầu</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Tiêu chí</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50" ht="29" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="29" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>NFR-01</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Tốc độ tải</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>&lt; 3 giây trên 4G; ảnh nén; không framework nặng</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51" ht="29" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="29" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>NFR-02</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Mobile &lt;768px, Tablet 768–1023px, Desktop ≥1024px</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr"/>
-      <c r="E51" s="6" t="inlineStr"/>
-      <c r="F51" s="6" t="inlineStr"/>
-    </row>
-    <row r="52" ht="29" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="29" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>NFR-03</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Chi phí</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>0đ giai đoạn đầu (Cloudflare Pages + Supabase Free)</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53" ht="29" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="29" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>NFR-04</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Bảo mật</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>Lead chỉ đọc sau đăng nhập (RLS); form public chỉ INSERT</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr"/>
-      <c r="E53" s="6" t="inlineStr"/>
-      <c r="F53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54" ht="29" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="29" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>NFR-05</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Dễ bảo trì</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Người không code sửa được nội dung theo hướng dẫn</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55" ht="29" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="29" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>NFR-06</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Trình duyệt</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>Chrome, Safari, Edge, trình duyệt trong app Zalo/Facebook</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr"/>
-      <c r="E55" s="6" t="inlineStr"/>
-      <c r="F55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56" ht="29" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="29" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>NFR-07</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Contrast WCAG AA, font ≥16px mobile, touch ≥44px</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>⚠ 6. Rà soát: Điểm mơ hồ / Edge case / Rủi ro</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Vấn đề</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>Đề xuất</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Loại</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60" ht="29" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61" ht="29" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Chưa có thông tin pháp lý (GPKD) ở footer</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Bổ sung khi có; quảng cáo ngành visa yêu cầu minh bạch</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr"/>
-    </row>
-    <row r="61" ht="29" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62" ht="29" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>SĐT trùng gửi form nhiều lần (spam)</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>Đã xử lý: chặn 60s phía client; admin lọc trùng</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>Edge case</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr"/>
-    </row>
-    <row r="62" ht="29" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63" ht="29" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>SĐT sai định dạng (+84, khoảng trắng)</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Đã xử lý: tự chuẩn hóa +84 → 0</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Edge case</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr"/>
-    </row>
-    <row r="63" ht="29" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64" ht="29" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Supabase Free pause sau 7 ngày không hoạt động</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>Vào dashboard hàng tuần; nâng cấp khi có doanh thu</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64" ht="29" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65" ht="29" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Giá dịch vụ chưa xác định (placeholder)</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Chốt bảng giá trước khi chạy quảng cáo</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr"/>
-    </row>
-    <row r="65" ht="29" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="29" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Số liệu '5000+ hồ sơ / 98% đậu' là placeholder</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>Thay số thật hoặc bỏ trước khi quảng cáo</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr"/>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Mất mạng lúc gửi form</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Đã xử lý: báo lỗi + gợi ý gọi hotline/Zalo</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Edge case</t>
         </is>
       </c>
-      <c r="E66" s="14" t="inlineStr">
+      <c r="E67" s="14" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A59:F59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2275,7 +3441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2325,7 +3491,7 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr"/>
     </row>
-    <row r="6" ht="16" customHeight="1">
+    <row r="6" ht="29" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>1</t>
@@ -2338,7 +3504,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Banner chính: H1, mô tả, CTA, badge số liệu</t>
+          <t>Banner chính: H1, mô tả, CTA, badge số liệu, cam kết đậu mới thu phí</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr"/>
@@ -2363,7 +3529,7 @@
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
     </row>
-    <row r="8" ht="29" customHeight="1">
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>3</t>
@@ -2376,7 +3542,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>6 lợi ích: nhanh, đậu cao, minh bạch, 24/7, trọn gói, bảo mật</t>
+          <t>6 lợi ích + banner cam kết đậu mới thu phí</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
@@ -2414,7 +3580,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>3 đánh giá khách hàng</t>
+          <t>Slider đánh giá khách hàng (dữ liệu thật từ Facebook)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr"/>
@@ -2496,588 +3662,607 @@
       <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>blog.html (đề xuất)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Trang blog công khai — xem sheet 09</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>2. Sitemap – Trang quản trị (admin.html) &amp; mở rộng tương lai</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Khu vực</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Trang/Tab</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Chức năng</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Supabase Auth (email + mật khẩu)</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Tab Khách đăng ký</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Xem, lọc, đổi trạng thái, xuất CSV</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Tab Bài viết</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Thêm / sửa / xóa bài viết</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Thêm / sửa / xóa bài viết — nguồn cho blog.html</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Tab Danh mục</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Thêm / xóa danh mục</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Tương lai</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Blog / Tin tức</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Trang bài viết công khai</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Blog công khai</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>blog.html — xem spec sheet 09</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Tương lai</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Chi tiết quốc gia</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>/visa-nhat-ban... phục vụ SEO</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Tương lai</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Đa ngôn ngữ</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>EN / JP</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>3. User Flow – Khách hàng (luồng chính)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Bước</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Hành động</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Chi tiết / Rẽ nhánh</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Vào trang</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Từ quảng cáo / Google / chia sẻ</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29" ht="29" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="29" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Xem banner + CTA</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Chưa rõ → cuộn xem Dịch vụ / Lợi ích / Đánh giá / FAQ rồi quay lại</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="29" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="29" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Chọn cách liên hệ</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Gấp → bấm nút nổi Gọi/Zalo/Facebook (kết nối trực tiếp ✅)</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Điền form</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Họ tên, SĐT, Quốc gia, Ghi chú</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Validate</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Sai → hiện lỗi ngay tại ô nhập, quay lại bước 4</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33" ht="29" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="29" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Gửi lên server</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Thành công → thông báo 'liên hệ trong 24h', lead lưu Supabase ✅</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Nếu lỗi mạng</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi + gợi ý gọi hotline/Zalo (không mất khách)</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>4. User Flow – Admin</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Bước</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Hành động</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Chi tiết</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Mở admin.html</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Nhập email + mật khẩu; sai → báo lỗi</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Tab Leads</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Xem danh sách, lọc theo trạng thái/quốc gia/tìm kiếm</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40" ht="29" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="29" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Gọi khách</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Bấm SĐT gọi trực tiếp → đổi trạng thái Mới/Đã gọi/Chốt/Hủy</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Xuất CSV</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Tải file mở bằng Excel (backup hàng tuần)</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Bài viết / Danh mục</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>CRUD nội dung</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>CRUD nội dung — nội dung mẫu xem sheet 09</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Đăng xuất</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Kết thúc phiên</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="6" t="inlineStr"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>5. Luồng dữ liệu &amp; bảo mật</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Form trên web dùng anon key chỉ có quyền GHI THÊM (INSERT) vào bảng leads — người ngoài không đọc được dữ liệu. Admin đăng nhập qua Supabase Auth mới được ĐỌC/SỬA. Cơ chế này là RLS (Row Level Security – bảo mật theo dòng dữ liệu).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>Form trên web dùng anon key chỉ có quyền GHI THÊM (INSERT) vào bảng leads — người ngoài không đọc được dữ liệu. Admin đăng nhập qua Supabase Auth mới được ĐỌC/SỬA. Cơ chế này là RLS (Row Level Security – bảo mật theo dòng dữ liệu). Riêng bảng posts đã có sẵn policy cho anon SELECT khi published=true — đây là cơ sở để xây trang blog công khai (sheet 09) mà không cần đổi schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>⚠ Rà soát</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Vấn đề</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Đề xuất</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Loại</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="29" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="51" ht="29" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>One-page khó SEO cho từng quốc gia</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Phase mở rộng: tách trang chi tiết khi cần SEO</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="29" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="52" ht="29" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Bấm Zalo trên PC không cài app</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Link zalo.me tự mở bản web — đã đúng hướng</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>Edge case</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="E52" s="14" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="29" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="53" ht="29" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Chưa có đo lường (analytics)</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Gắn Google Analytics / Meta Pixel trước khi chạy quảng cáo</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
@@ -3086,14 +4271,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3298,7 +4483,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" ht="29" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Đánh giá</t>
@@ -3306,22 +4491,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Grid 3 cột</t>
+          <t>Slider 1 thẻ giữa trang, max 700px</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Grid 2 cột</t>
+          <t>Như desktop</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>1 cột</t>
+          <t>Full-width, mũi tên nhỏ hơn</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>5 sao + quote + avatar chữ cái</t>
+          <t>Bấm Next/Prev, chấm tròn, vuốt tay</t>
         </is>
       </c>
     </row>
@@ -3581,7 +4766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4226,7 +5411,7 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4. Component list (16 component)</t>
+          <t>4. Component list (18 component)</t>
         </is>
       </c>
     </row>
@@ -4344,10 +5529,10 @@
       </c>
       <c r="E43" s="5" t="inlineStr"/>
     </row>
-    <row r="44" ht="29" customHeight="1">
+    <row r="44" ht="16" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Card lợi ích / đánh giá</t>
+          <t>Card lợi ích</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -4358,7 +5543,7 @@
       <c r="C44" s="6" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Icon tròn / 5 sao + avatar chữ cái</t>
+          <t>Icon tròn nền xanh nhạt</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr"/>
@@ -4366,75 +5551,75 @@
     <row r="45" ht="29" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Navbar</t>
+          <t>Reviews Slider</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Top / Scrolled / Mobile</t>
+          <t>1 thẻ/lần, loop vô hạn</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Sticky; hamburger trượt xuống</t>
+          <t>Next/Prev, dot, vuốt tay, tự chạy 6s, dừng khi hover</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr"/>
     </row>
-    <row r="46" ht="16" customHeight="1">
+    <row r="46" ht="29" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Navbar</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>1 kiểu</t>
+          <t>Top / Scrolled / Mobile</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr"/>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>4 cột desktop / 1 cột mobile</t>
+          <t>Sticky; hamburger trượt xuống; scrollspy active link</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr"/>
     </row>
-    <row r="47" ht="29" customHeight="1">
+    <row r="47" ht="16" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Form đăng ký</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Default / Submitting / Success / Error</t>
+          <t>1 kiểu</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Validate client; chống spam 60s; thành công thay bằng ✓</t>
+          <t>4 cột desktop / 1 cột mobile</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr"/>
     </row>
-    <row r="48" ht="16" customHeight="1">
+    <row r="48" ht="29" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Form đăng ký</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Success / Error</t>
+          <t>Default / Submitting / Success / Error</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr"/>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Trượt lên giữa dưới, tự ẩn 5s</t>
+          <t>Validate client; chống spam 60s; thành công thay bằng ✓</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
@@ -4442,56 +5627,56 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>FAQ Accordion</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Đóng / Mở</t>
+          <t>Success / Error</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Mũi tên xoay; không tự đóng câu cũ</t>
+          <t>Trượt lên giữa dưới, tự ẩn 5s</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr"/>
     </row>
-    <row r="50" ht="29" customHeight="1">
+    <row r="50" ht="16" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Banner Hero</t>
+          <t>FAQ Accordion</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Desktop 2 cột / Mobile 1 cột</t>
+          <t>Đóng / Mở</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr"/>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>H1 + CTA + badge số liệu</t>
+          <t>Mũi tên xoay; không tự đóng câu cũ</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr"/>
     </row>
-    <row r="51" ht="16" customHeight="1">
+    <row r="51" ht="29" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Floating Contact</t>
+          <t>Banner Hero</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Thu gọn / Bung</t>
+          <t>Desktop 2 cột / Mobile 1 cột</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr"/>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>3 nút Gọi/Zalo/Facebook; mobile ≥48px</t>
+          <t>H1 + CTA + badge số liệu + USP đậu mới thu phí</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr"/>
@@ -4499,18 +5684,18 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Floating Contact</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Ngang / Dọc</t>
+          <t>Thu gọn / Bung</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr"/>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>4 bước đánh số</t>
+          <t>3 nút Gọi/Zalo/Facebook; mobile ≥48px</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr"/>
@@ -4518,18 +5703,18 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Badge</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>1 kiểu</t>
+          <t>Ngang / Dọc</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr"/>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>'✓ 5000+ hồ sơ'...</t>
+          <t>4 bước đánh số</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr"/>
@@ -4537,7 +5722,7 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>QR box</t>
+          <t>Badge</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -4548,121 +5733,159 @@
       <c r="C54" s="6" t="inlineStr"/>
       <c r="D54" s="6" t="inlineStr">
         <is>
+          <t>'✓ 5000+ hồ sơ'...</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>QR box</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>1 kiểu</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
           <t>QR Zalo trong form + footer</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr"/>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>USP Banner/Highlight</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>1 kiểu</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Cam kết đậu visa mới thu phí dịch vụ</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>⚠ Rà soát</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Vấn đề</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Đề xuất</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Loại</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="58" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="60" ht="58" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Emoji cờ hiển thị khác nhau giữa hệ điều hành</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Chấp nhận giai đoạn đầu; nâng cấp SVG flagcdn.com sau</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Edge case</t>
         </is>
       </c>
-      <c r="E58" s="14" t="inlineStr">
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="43.5" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
+    <row r="61" ht="43.5" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Số liệu badge là placeholder</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>Thay số thật trước khi chạy quảng cáo</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="29" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="62" ht="29" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Google Fonts cần mạng</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Đã có fallback system-ui</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Edge case</t>
         </is>
       </c>
-      <c r="E60" s="14" t="inlineStr">
+      <c r="E62" s="14" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -4676,7 +5899,7 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4689,7 +5912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4835,7 +6058,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>8 section, responsive, validate, nút nổi</t>
+          <t>8 section, responsive, validate, nút nổi, USP, slider đánh giá</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -4899,7 +6122,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Test trên Supabase Cloud thật (không Docker), chạy 14 test case</t>
+          <t>Test trên Supabase Cloud thật (không Docker), chạy test case</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -4945,350 +6168,350 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="12" ht="29" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Blog công khai (mở rộng)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>blog.html hiển thị bài viết — xem sheet 09</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Xây dựng sau khi Phase 1-6 ổn định</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2-3 ngày</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>☐ Chưa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Ghi chú Phase 4-5: code (admin.html + supabase_setup.sql) đã viết xong, nhưng CHƯA chạy — còn thiếu bước tạo project Supabase thật và điền SUPABASE_URL/ANON_KEY. Test trực tiếp trên Supabase Cloud (Free), KHÔNG dùng Docker/Supabase local. Xem sheet 08_Bàn giao Claude Code và 01_Docs/07_Huong_dan_Deploy.md Bước 2.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Checklist việc CÒN LẠI của bạn (Phase 4→6)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Việc</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Hướng dẫn tại</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="29" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="17" ht="29" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Tạo tài khoản Supabase, chạy supabase_setup.sql</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>07_Deploy – Bước 1</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>☐ Chưa</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="29" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="18" ht="29" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Điền SUPABASE_URL + ANON_KEY vào 2 file HTML</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>07_Deploy – Bước 1.7</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>☐ Chưa</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="43.5" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19" ht="43.5" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Gửi thử form → thấy lead trong admin (test thẳng trên Cloud)</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>07_Deploy – Bước 2</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>☐ Chưa</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20" ht="43.5" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Chạy 14 test case (bảng dưới), 100% High phải Pass</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Chạy các test case (bảng dưới), 100% High phải Pass</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Sheet này</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>☐ Chưa</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="43.5" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="21" ht="43.5" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Deploy Cloudflare Pages (kéo thả 2 HTML + folder assets)</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>07_Deploy – Bước 3</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>☐ Chưa</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="43.5" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22" ht="43.5" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Thay placeholder còn lại: giá, số liệu, review, GPKD</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>README</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>☐ Chưa</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="29" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="23" ht="29" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>(Tùy chọn) Mua domain + trỏ DNS</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>07_Deploy – Bước 4</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>☐ Chưa</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="43.5" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24" ht="43.5" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Đặt lịch hàng tuần: xem lead + xuất CSV + vào Supabase</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>07_Deploy – Bước 7</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>☐ Chưa</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="25" ht="29" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>(Mở rộng) Duyệt nội dung + triển khai blog.html</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Sheet 09</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>☐ Chưa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Test case (điền Actual Result khi kiểm thử)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TC-001</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Chrome PC</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Cuộn toàn trang</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Đủ 8 section, không vỡ layout</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28" ht="29" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>TC-002</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Điện thoại / DevTools mobile</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Cuộn + bấm menu</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Hamburger hoạt động, không tràn ngang</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TC-003</t>
+          <t>TC-001</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Form đăng ký</t>
+          <t>Chrome PC</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Bỏ trống Họ tên, Gửi</t>
+          <t>Cuộn toàn trang</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Báo lỗi, không gửi</t>
+          <t>Đủ 8 section, không vỡ layout</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -5298,25 +6521,25 @@
       </c>
       <c r="F29" s="5" t="inlineStr"/>
     </row>
-    <row r="30" ht="16" customHeight="1">
+    <row r="30" ht="29" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>TC-004</t>
+          <t>TC-002</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Form đăng ký</t>
+          <t>Điện thoại / DevTools mobile</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>SĐT '12345', Gửi</t>
+          <t>Cuộn + bấm menu</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Báo lỗi SĐT không hợp lệ</t>
+          <t>Hamburger hoạt động, không tràn ngang</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -5329,7 +6552,7 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TC-005</t>
+          <t>TC-003</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -5339,40 +6562,40 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>SĐT '+84 912 345 678'</t>
+          <t>Bỏ trống Họ tên, Gửi</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Tự chuẩn hóa 0912345678, gửi OK</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Báo lỗi, không gửi</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
     </row>
-    <row r="32" ht="29" customHeight="1">
+    <row r="32" ht="16" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>TC-006</t>
+          <t>TC-004</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Đã cấu hình Supabase Cloud</t>
+          <t>Form đăng ký</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Điền form hợp lệ, Gửi</t>
+          <t>SĐT '12345', Gửi</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Thông báo thành công; lead trong admin</t>
+          <t>Báo lỗi SĐT không hợp lệ</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -5385,22 +6608,22 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TC-007</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Vừa gửi xong</t>
+          <t>Form đăng ký</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Gửi lại ngay</t>
+          <t>SĐT '+84 912 345 678'</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Bị chặn 60s, báo 'vui lòng chờ'</t>
+          <t>Tự chuẩn hóa 0912345678, gửi OK</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -5413,12 +6636,12 @@
     <row r="34" ht="29" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>TC-008</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Chưa cấu hình Supabase</t>
+          <t>Đã cấu hình Supabase Cloud</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -5428,12 +6651,12 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Báo lỗi thân thiện + gợi ý hotline/Zalo</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Thông báo thành công; lead trong admin</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr"/>
@@ -5441,27 +6664,27 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TC-009</t>
+          <t>TC-007</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Mở admin.html</t>
+          <t>Vừa gửi xong</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Đăng nhập sai mật khẩu</t>
+          <t>Gửi lại ngay</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Báo lỗi, không vào được</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Bị chặn 60s, báo 'vui lòng chờ'</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
@@ -5469,111 +6692,111 @@
     <row r="36" ht="29" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
+          <t>TC-008</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Chưa cấu hình Supabase</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Điền form hợp lệ, Gửi</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Báo lỗi thân thiện + gợi ý hotline/Zalo</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TC-009</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Mở admin.html</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Đăng nhập sai mật khẩu</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Báo lỗi, không vào được</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="29" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
           <t>TC-010</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Đã đăng nhập admin</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Bấm Xuất CSV</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>File .csv mở Excel đúng, không lỗi font Việt</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37" ht="29" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="29" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>TC-011</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Đã đăng nhập admin</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Thêm→sửa→xóa 1 bài viết</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Thao tác thành công, danh sách cập nhật</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>TC-012</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Trên mobile</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Bấm nút Gọi/Zalo/Facebook</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Mở đúng app tương ứng</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>TC-013</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Bấm từng câu hỏi</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Mở/đóng mượt</t>
-        </is>
-      </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
@@ -5581,119 +6804,231 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Trên mobile</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Bấm nút Gọi/Zalo/Facebook</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Mở đúng app tương ứng</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TC-013</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Bấm từng câu hỏi</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Mở/đóng mượt</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
           <t>TC-014</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Mạng chậm/mất mạng</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Gửi form</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Báo lỗi rõ, không treo nút Gửi</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="29" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TC-015</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Section đánh giá</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Bấm nút Next/Prev nhiều lần</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Chuyển slide đúng thứ tự, loop lại từ đầu/cuối</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="29" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Section đánh giá trên mobile</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Vuốt trái/phải</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Chuyển slide theo hướng vuốt</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>⚠ Rủi ro tiến độ</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Rủi ro</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Đề xuất</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-    </row>
-    <row r="44" ht="29" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" ht="29" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Thiếu bảng giá/số liệu thật làm chậm go-live</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Deploy trước trên *.pages.dev, công khai sau khi thay</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45" ht="29" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="29" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Chưa quen Supabase</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Làm đúng từng bước trong 07_Deploy, chỉ thao tác dashboard</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6584,7 +7919,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Project Settings → API → copy 2 giá trị</t>
+          <t>Project Settings → API Keys → copy Publishable key + Project URL (Integrations → Data API)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -6712,7 +8047,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>⚠ Quan trọng: chỉ dùng anon public key. KHÔNG BAO GIỜ đặt service_role key vào file HTML.</t>
+          <t>⚠ Quan trọng: chỉ dùng Publishable key (hoặc anon public key nếu dùng tab Legacy). KHÔNG BAO GIỜ đặt Secret key (sb_secret_...) hay service_role key vào file HTML.</t>
         </is>
       </c>
     </row>
@@ -6833,7 +8168,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Chạy 14 test case ở sheet 05_Kế hoạch</t>
+          <t>Chạy test case ở sheet 05_Kế hoạch</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -7576,7 +8911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7672,7 +9007,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>index.html — đã gắn logo/hotline/Zalo/Facebook/địa chỉ thật</t>
+          <t>index.html — đã gắn logo/hotline/Zalo/Facebook/địa chỉ thật + USP + slider đánh giá</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -7710,7 +9045,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>14 test case tại sheet 05_Kế hoạch — test trên Supabase Cloud thật</t>
+          <t>Test case tại sheet 05_Kế hoạch — test trên Supabase Cloud thật</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -7740,333 +9075,337 @@
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="6" t="inlineStr"/>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="12" ht="29" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>6.5 Blog công khai</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Tài liệu spec đã có ở sheet 09 — CHƯA code</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>☐ Chưa</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2. Tech stack — GIỮ NGUYÊN triết lý khi phát triển tiếp</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Lớp</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Lựa chọn</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Lý do — KHÔNG tự ý đổi nếu chưa hỏi người dùng</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15" ht="43.5" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="43.5" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Front-end</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>HTML/CSS/JS thuần, 1 file/trang, không framework, không build step</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Người vận hành không biết code → phải mở file là chạy được, không npm install</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="43.5" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="43.5" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Back-end</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Supabase (PostgreSQL + Auth + REST tự động qua PostgREST)</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Gọi thẳng bằng fetch(), không cần SDK/npm package</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="29" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="29" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Hosting</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Cloudflare Pages (static, kéo thả, miễn phí)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Khớp với mô hình 1 file HTML, không cần server riêng</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="43.5" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="43.5" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Test trực tiếp trên Supabase Cloud (Free) — KHÔNG dùng Docker/Supabase CLI local</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Người dùng không rành Docker; Cloud Free đủ dùng và khớp 100% với bản go-live</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>⚠ Không thêm React/Vue/Vite/webpack hay bất kỳ bundler nào trừ khi người dùng yêu cầu rõ — sẽ phá vỡ quy trình deploy kéo-thả hiện tại. Không đề xuất lại Docker/Supabase local — quyết định đã chốt. Không đề xuất đổi sang SQL Server/SSMS (khác engine, phá vỡ kiến trúc Auth + API tự sinh).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>⚠ Không thêm React/Vue/Vite/webpack hay bất kỳ bundler nào trừ khi người dùng yêu cầu rõ — sẽ phá vỡ quy trình deploy kéo-thả hiện tại. Không đề xuất lại Docker/Supabase local — quyết định đã chốt. Không đề xuất đổi sang SQL Server/SSMS (khác engine, phá vỡ kiến trúc Auth + API tự sinh). Tính năng Trang Blog công khai (sheet 09) PHẢI dùng cùng triết lý này (HTML thuần, fetch() trực tiếp).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>3. Bản đồ file dự án</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Đường dẫn</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Vai trò</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="29" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="29" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>CLAUDE.md</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Context đầy đủ cho agent (đọc trước khi sửa gì)</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="29" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="29" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>README.md</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Hướng dẫn cho người dùng (không phải agent)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="29" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="29" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>01_Docs/*.md + .xlsx</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Tài liệu thiết kế/kế hoạch — nguồn sự thật cho spec</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26" ht="29" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="29" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>02_Source/index.html</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Landing page — TOÀN BỘ code trong 1 file</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="29" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="29" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>02_Source/admin.html</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Trang quản trị — TOÀN BỘ code trong 1 file</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28" ht="43.5" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="43.5" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>02_Source/supabase_setup.sql</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Script tạo bảng leads/posts/categories + RLS (idempotent)</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr"/>
-      <c r="D28" s="6" t="inlineStr"/>
-      <c r="E28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29" ht="43.5" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="43.5" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>02_Source/assets/</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>logo.png, favicon.png, qr-zalo.png — đã xử lý sẵn, không sửa lại</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30" ht="43.5" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="43.5" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>02_Source/blog.html (CHƯA có)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>File cần tạo mới theo spec sheet 09 khi triển khai Phase 6.5</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="43.5" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>03_Information/Information.md</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>NGUỒN DỮ LIỆU THẬT DUY NHẤT: tên công ty, SĐT, địa chỉ, email, Facebook</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr"/>
-      <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="6" t="inlineStr"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>4. Nơi cấu hình dữ liệu công ty (đầu file index.html, dòng ~18–25)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Hằng số</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Giá trị hiện tại</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34" ht="29" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="29" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>SUPABASE_URL</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>(trống — cần điền theo 07_Huong_dan_Deploy.md Bước 1)</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>SUPABASE_ANON_KEY</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>(trống — cần điền)</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr"/>
-      <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>HOTLINE / ZALO_PHONE</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>0935887922</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="5" t="inlineStr"/>
       <c r="E36" s="5" t="inlineStr"/>
     </row>
-    <row r="37" ht="29" customHeight="1">
+    <row r="37" ht="16" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>FACEBOOK_URL</t>
+          <t>SUPABASE_ANON_KEY</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/share/1EVr8W3p2E/</t>
+          <t>(trống — cần điền)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr"/>
@@ -8076,133 +9415,125 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>COMPANY_NAME</t>
+          <t>HOTLINE / ZALO_PHONE</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Top Visa</t>
+          <t>0935887922</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="5" t="inlineStr"/>
       <c r="E38" s="5" t="inlineStr"/>
     </row>
-    <row r="39" ht="16" customHeight="1">
+    <row r="39" ht="29" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>COMPANY_EMAIL</t>
+          <t>FACEBOOK_URL</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>hien.gotravel@gmail.com</t>
+          <t>https://www.facebook.com/share/1EVr8W3p2E/</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
       <c r="E39" s="6" t="inlineStr"/>
     </row>
-    <row r="40" ht="29" customHeight="1">
+    <row r="40" ht="16" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>COMPANY_ADDRESS</t>
+          <t>COMPANY_NAME</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>303 Âu Cơ, Liên Chiểu, Đà Nẵng</t>
+          <t>Top Visa</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="5" t="inlineStr"/>
       <c r="E40" s="5" t="inlineStr"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>admin.html có khối tương tự (chỉ SUPABASE_URL + ANON_KEY, đầu file) — phải giống hệt index.html. Nếu Information.md thay đổi, đồng bộ lại các hằng số này và title/meta/footer liên quan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>COMPANY_EMAIL</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>hien.gotravel@gmail.com</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr"/>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42" ht="29" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>COMPANY_ADDRESS</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>303 Âu Cơ, Liên Chiểu, Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>admin.html có khối tương tự (chỉ SUPABASE_URL + ANON_KEY, đầu file) — phải giống hệt index.html. Nếu Information.md thay đổi, đồng bộ lại các hằng số này và title/meta/footer liên quan. blog.html khi tạo mới cũng phải dùng đúng 2 khóa Supabase này.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>5. Việc còn thiếu — KHÔNG tự bịa, hỏi lại người dùng nếu cần</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Vị trí</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr"/>
-      <c r="E44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Badge hero</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>'5000+ hồ sơ', '98% đậu'</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Cao — số liệu ảnh hưởng chính sách quảng cáo</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Section dịch vụ</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Giá 'Từ x đ' mỗi quốc gia</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="6" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr"/>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Section đánh giá</t>
+          <t>Badge hero</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>3 review mẫu</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>Trung bình</t>
+          <t>'5000+ hồ sơ', '98% đậu'</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Cao — số liệu ảnh hưởng chính sách quảng cáo</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr"/>
@@ -8211,17 +9542,17 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Section dịch vụ</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Số GPKD</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Trung bình — chưa có trong Information.md</t>
+          <t>Giá 'Từ x đ' mỗi quốc gia</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Cao</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -8230,113 +9561,121 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Cả 2 file HTML</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>SUPABASE_URL / ANON_KEY</t>
+          <t>Số GPKD</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Cao — chặn toàn bộ form + admin hoạt động</t>
+          <t>Trung bình — chưa có trong Information.md</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr"/>
       <c r="E49" s="5" t="inlineStr"/>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Cả 2 file HTML</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>SUPABASE_URL / ANON_KEY</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Cao — chặn toàn bộ form + admin hoạt động</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51" ht="29" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Ảnh minh họa cho blog (sheet 09)</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Chưa xác nhận bản quyền ảnh nguồn Facebook</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Cao — xem rà soát sheet 09</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>6. Việc KHÔNG được làm</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Quy tắc</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53" ht="43.5" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55" ht="43.5" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Không thêm framework/bundler — phá vỡ mô hình 1 file HTML deploy trực tiếp</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr"/>
-      <c r="E53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54" ht="43.5" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Không đặt service_role key của Supabase vào file HTML (chỉ dùng anon public key)</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr"/>
-      <c r="D54" s="6" t="inlineStr"/>
-      <c r="E54" s="6" t="inlineStr"/>
-    </row>
-    <row r="55" ht="29" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Không tự bịa số liệu/giá/review/thông tin pháp lý</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr"/>
       <c r="D55" s="5" t="inlineStr"/>
       <c r="E55" s="5" t="inlineStr"/>
     </row>
-    <row r="56" ht="58" customHeight="1">
+    <row r="56" ht="43.5" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Không đổi tên index.html/admin.html hay cấu trúc assets/ mà không cập nhật 07_Huong_dan_Deploy.md</t>
+          <t>Không đặt service_role key của Supabase vào file HTML (chỉ dùng anon public key)</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr"/>
       <c r="D56" s="6" t="inlineStr"/>
       <c r="E56" s="6" t="inlineStr"/>
     </row>
-    <row r="57" ht="43.5" customHeight="1">
+    <row r="57" ht="29" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Không xóa comment [THAY_THẾ] cho tới khi giá trị thật đã điền</t>
+          <t>Không tự bịa số liệu/giá/review/thông tin pháp lý</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr"/>
@@ -8346,113 +9685,158 @@
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Không đề xuất lại Docker/Supabase local, không đề xuất SQL Server/SSMS thay Supabase</t>
+          <t>Không đổi tên index.html/admin.html hay cấu trúc assets/ mà không cập nhật 07_Huong_dan_Deploy.md</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr"/>
       <c r="D58" s="6" t="inlineStr"/>
       <c r="E58" s="6" t="inlineStr"/>
     </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="59" ht="43.5" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Không xóa comment [THAY_THẾ] cho tới khi giá trị thật đã điền</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60" ht="58" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Không đề xuất lại Docker/Supabase local, không đề xuất SQL Server/SSMS thay Supabase</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61" ht="58" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Không tự tải/dùng ảnh từ Facebook công ty khi chưa xác minh bản quyền — xem rà soát sheet 09</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>7. Cách kiểm tra sau khi sửa code (không có test framework)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Bước kiểm tra</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr"/>
-      <c r="D61" s="4" t="inlineStr"/>
-      <c r="E61" s="4" t="inlineStr"/>
-    </row>
-    <row r="62" ht="43.5" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65" ht="43.5" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra thẻ HTML cân bằng + cú pháp JS bằng node --check trên phần &lt;script&gt;</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr"/>
-    </row>
-    <row r="63" ht="43.5" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr"/>
+      <c r="D65" s="5" t="inlineStr"/>
+      <c r="E65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="43.5" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>Mở file bằng trình duyệt, thử theo 14 test case ở sheet 05_Kế hoạch</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr"/>
-      <c r="D63" s="6" t="inlineStr"/>
-      <c r="E63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64" ht="72.5" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Mở file bằng trình duyệt, thử theo test case ở sheet 05_Kế hoạch</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr"/>
+      <c r="D66" s="6" t="inlineStr"/>
+      <c r="E66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67" ht="72.5" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Test luôn trên Supabase Cloud thật (không Docker): gửi 1 lead thử → kiểm tra hiện trong Table Editor / admin.html</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr"/>
-      <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr"/>
-    </row>
-    <row r="65" ht="58" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68" ht="58" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Trước khi báo 'xong': xác nhận không còn placeholder mới bị bỏ sót, không có dữ liệu tự bịa</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr"/>
-      <c r="D65" s="6" t="inlineStr"/>
-      <c r="E65" s="6" t="inlineStr"/>
+      <c r="C68" s="6" t="inlineStr"/>
+      <c r="D68" s="6" t="inlineStr"/>
+      <c r="E68" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A63:E63"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/01_Docs/Visa-Landing-Page_Tai_lieu.xlsx
+++ b/01_Docs/Visa-Landing-Page_Tai_lieu.xlsx
@@ -8931,7 +8931,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dùng khi tiếp tục phát triển dự án bằng Claude Code | Xem đầy đủ tại CLAUDE.md ở thư mục gốc dự án | Cập nhật 2026-07-18</t>
+          <t>Dùng khi tiếp tục phát triển dự án bằng Claude Code | Xem đầy đủ tại CLAUDE.md ở thư mục gốc dự án | Cập nhật 2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9026,12 +9026,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>admin.html + supabase_setup.sql viết xong — CHƯA chạy (thiếu SUPABASE_URL/ANON_KEY)</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>☐ Chưa</t>
+          <t>admin.html + supabase_setup.sql — ĐÃ CHẠY THẬT, SUPABASE_URL/ANON_KEY đã điền (xem 08_Ban_giao_Claude_Code.md)</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>✓ Xong</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr"/>
@@ -9045,12 +9045,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Test case tại sheet 05_Kế hoạch — test trên Supabase Cloud thật</t>
+          <t>Đã test thủ công 1 phần (gửi lead thật, đăng nhập/đăng bài admin) — CHƯA chạy đủ 14 test case chính thức sheet 05_Kế hoạch</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>☐ Chưa</t>
+          <t>☐ Một phần</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr"/>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Chưa đưa lên Cloudflare Pages</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>☐ Chưa</t>
+          <t>Đã deploy thật qua Cloudflare Workers (không phải Pages) — https://topvisa.nguyennc1357.workers.dev</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>✓ Xong</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
@@ -9083,12 +9083,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Tài liệu spec đã có ở sheet 09 — CHƯA code</t>
+          <t>Đã làm bản rút gọn (section Tin tức trong index.html, không phải blog.html riêng như spec) — xem 08_Ban_giao_Claude_Code.md mục 6</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>☐ Chưa</t>
+          <t>☐ Một phần</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>(trống — cần điền theo 07_Huong_dan_Deploy.md Bước 1)</t>
+          <t>https://vvnjxvcdnzttcdufjjgo.supabase.co (đã điền thật)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr"/>
@@ -9400,12 +9400,12 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>SUPABASE_ANON_KEY</t>
+          <t>SUPABASE_ANON_KEY (Publishable key)</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>(trống — cần điền)</t>
+          <t>sb_publishable_mp5Q5GRLV_ll8E4eNeivWw_aUv0q0xR (đã điền thật, an toàn public)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr"/>
